--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_cell_labels.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_cell_labels.xlsx
@@ -594,53 +594,53 @@
         <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>31.68068814277649</v>
+        <v>34.32987022399902</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7799999713897705</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0298550770832941</v>
+        <v>0.029522065932934</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6237220168113708</v>
+        <v>0.639243483543396</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6237220168113708</v>
+        <v>0.639243483543396</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6238551139831543</v>
+        <v>0.6395139098167419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6142097115516663</v>
+        <v>0.6398996114730835</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0306000709533691</v>
+        <v>0.0333278179168701</v>
       </c>
       <c r="K2" t="n">
-        <v>16.90618276596069</v>
+        <v>17.3544340133667</v>
       </c>
       <c r="L2" t="n">
-        <v>1.017329454421997</v>
+        <v>0.968569040298462</v>
       </c>
       <c r="M2" t="n">
-        <v>2.320980548858643</v>
+        <v>2.431927442550659</v>
       </c>
       <c r="N2" t="n">
-        <v>2.899599552154541</v>
+        <v>3.069146156311035</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1695549090703328</v>
+        <v>0.161428173383077</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3868300914764404</v>
+        <v>0.4053212404251098</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4832665920257568</v>
+        <v>0.5115243593851725</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-115444</t>
+          <t>20250720-044000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>35.06394863128662</v>
+        <v>34.00672602653503</v>
       </c>
       <c r="D3" t="n">
         <v>0.7799999713897705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.030322606103462</v>
+        <v>0.0298300935671879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6465951204299927</v>
+        <v>0.6566990613937378</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6465951204299927</v>
+        <v>0.6566990613937378</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6476783156394958</v>
+        <v>0.6574235558509827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6464569568634033</v>
+        <v>0.6397659778594971</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0305736064910888</v>
+        <v>0.0321640968322753</v>
       </c>
       <c r="K3" t="n">
-        <v>16.96841764450073</v>
+        <v>17.54133725166321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9753031730651855</v>
+        <v>1.002272129058838</v>
       </c>
       <c r="M3" t="n">
-        <v>2.369611263275146</v>
+        <v>2.373407602310181</v>
       </c>
       <c r="N3" t="n">
-        <v>2.936012029647827</v>
+        <v>3.055575370788574</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1625505288441976</v>
+        <v>0.1670453548431396</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3949352105458577</v>
+        <v>0.3955679337183634</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4893353382746379</v>
+        <v>0.5092625617980957</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-115626</t>
+          <t>20250720-044146</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -836,53 +836,53 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>34.65000581741333</v>
+        <v>36.24293303489685</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7799999713897705</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E4" t="n">
-        <v>0.029347913307056</v>
+        <v>0.0290867341192144</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6476195454597473</v>
+        <v>0.6277965903282166</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6476195454597473</v>
+        <v>0.6277965903282166</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6492990255355835</v>
+        <v>0.6266106963157654</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6379058957099915</v>
+        <v>0.6028972268104553</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0304784774780273</v>
+        <v>0.0406644344329834</v>
       </c>
       <c r="K4" t="n">
-        <v>16.87205457687378</v>
+        <v>17.2536153793335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9573557376861572</v>
+        <v>1.011214733123779</v>
       </c>
       <c r="M4" t="n">
-        <v>2.327754974365234</v>
+        <v>2.427031278610229</v>
       </c>
       <c r="N4" t="n">
-        <v>2.892653226852417</v>
+        <v>3.035638570785522</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1595592896143595</v>
+        <v>0.1685357888539632</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3879591623942057</v>
+        <v>0.4045052131017049</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4821088711420695</v>
+        <v>0.505939761797587</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-115811</t>
+          <t>20250720-044332</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>35.39192485809326</v>
+        <v>34.44605755805969</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6600000262260437</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0294782885333947</v>
+        <v>0.0298231152387765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6247433423995972</v>
+        <v>0.6562966108322144</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6247433423995972</v>
+        <v>0.6562966108322144</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6254188418388367</v>
+        <v>0.6570454835891724</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6049821972846985</v>
+        <v>0.6467530727386475</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0360441207885742</v>
+        <v>0.0315554141998291</v>
       </c>
       <c r="K5" t="n">
-        <v>16.82289385795593</v>
+        <v>17.35628247261047</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9901530742645264</v>
+        <v>0.9945504665374756</v>
       </c>
       <c r="M5" t="n">
-        <v>2.359774351119995</v>
+        <v>2.411879777908325</v>
       </c>
       <c r="N5" t="n">
-        <v>3.000685453414917</v>
+        <v>3.048125028610229</v>
       </c>
       <c r="O5" t="n">
-        <v>0.165025512377421</v>
+        <v>0.1657584110895792</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3932957251866658</v>
+        <v>0.4019799629847209</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5001142422358195</v>
+        <v>0.508020838101705</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-115956</t>
+          <t>20250720-044521</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C6" t="n">
-        <v>34.92720317840576</v>
+        <v>33.71496987342834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6600000262260437</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0294851462046304</v>
+        <v>0.0294001973592317</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6321667432785034</v>
+        <v>0.6564586758613586</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6321667432785034</v>
+        <v>0.6564586758613586</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6324883103370667</v>
+        <v>0.6576645970344543</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6225314140319824</v>
+        <v>0.6522453427314758</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0309624671936035</v>
+        <v>0.0326282978057861</v>
       </c>
       <c r="K6" t="n">
-        <v>16.77955794334412</v>
+        <v>17.24863576889038</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9692280292510986</v>
+        <v>1.008092164993286</v>
       </c>
       <c r="M6" t="n">
-        <v>2.335066795349121</v>
+        <v>2.453896284103394</v>
       </c>
       <c r="N6" t="n">
-        <v>2.952139377593994</v>
+        <v>3.060220718383789</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1615380048751831</v>
+        <v>0.1680153608322143</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3891777992248535</v>
+        <v>0.4089827140172322</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.492023229598999</v>
+        <v>0.5100367863972982</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-120142</t>
+          <t>20250720-044707</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C2" t="n">
-        <v>45.8185122013092</v>
+        <v>55.41064095497131</v>
       </c>
       <c r="D2" t="n">
-        <v>1.879999995231628</v>
+        <v>1.840000033378601</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1494888732066521</v>
+        <v>0.1568329093836936</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7644113302230835</v>
+        <v>0.7415280938148499</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7644113302230835</v>
+        <v>0.7415280938148499</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7682816386222839</v>
+        <v>0.7439950704574585</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7639589309692383</v>
+        <v>0.7357286810874939</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0576674938201904</v>
+        <v>0.0621159076690673</v>
       </c>
       <c r="K2" t="n">
-        <v>20.45311546325684</v>
+        <v>27.32370924949646</v>
       </c>
       <c r="L2" t="n">
-        <v>1.465471267700195</v>
+        <v>1.251915693283081</v>
       </c>
       <c r="M2" t="n">
-        <v>2.854852676391602</v>
+        <v>2.952176332473755</v>
       </c>
       <c r="N2" t="n">
-        <v>5.094837427139282</v>
+        <v>5.09554934501648</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2442452112833658</v>
+        <v>0.2086526155471801</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4758087793986003</v>
+        <v>0.4920293887456258</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8491395711898804</v>
+        <v>0.8492582241694132</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-120052</t>
+          <t>20250718-082550</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1486,53 +1486,53 @@
         <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>47.91454887390137</v>
+        <v>49.9752824306488</v>
       </c>
       <c r="D3" t="n">
         <v>1.840000033378601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1502773005228776</v>
+        <v>0.159157762160668</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7473085522651672</v>
+        <v>0.7878544926643372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7473085522651672</v>
+        <v>0.7878544926643372</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7486791610717773</v>
+        <v>0.7924606800079346</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7319438457489014</v>
+        <v>0.7743946313858032</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0590465068817138</v>
+        <v>0.0595805644989013</v>
       </c>
       <c r="K3" t="n">
-        <v>20.6702299118042</v>
+        <v>27.28975605964661</v>
       </c>
       <c r="L3" t="n">
-        <v>1.15706992149353</v>
+        <v>1.228995561599731</v>
       </c>
       <c r="M3" t="n">
-        <v>2.829883098602295</v>
+        <v>2.977825403213501</v>
       </c>
       <c r="N3" t="n">
-        <v>4.785656452178955</v>
+        <v>5.015619039535522</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1928449869155883</v>
+        <v>0.2048325935999552</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4716471831003825</v>
+        <v>0.4963042338689168</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7976094086964926</v>
+        <v>0.8359365065892538</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-120314</t>
+          <t>20250718-082825</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C4" t="n">
-        <v>46.28423881530762</v>
+        <v>50.67975687980652</v>
       </c>
       <c r="D4" t="n">
         <v>1.840000033378601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1521759124902578</v>
+        <v>0.1565438673036907</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6733287572860718</v>
+        <v>0.7277190089225769</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6733287572860718</v>
+        <v>0.7277190089225769</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6759974360466003</v>
+        <v>0.7314742803573608</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6745070815086365</v>
+        <v>0.7319223880767822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0663955211639404</v>
+        <v>0.0654671192169189</v>
       </c>
       <c r="K4" t="n">
-        <v>26.50275826454162</v>
+        <v>26.8362774848938</v>
       </c>
       <c r="L4" t="n">
-        <v>1.445028305053711</v>
+        <v>1.330915212631226</v>
       </c>
       <c r="M4" t="n">
-        <v>3.176631450653076</v>
+        <v>2.95327091217041</v>
       </c>
       <c r="N4" t="n">
-        <v>5.170124053955078</v>
+        <v>5.074068546295166</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2408380508422851</v>
+        <v>0.2218192021052042</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5294385751088461</v>
+        <v>0.4922118186950683</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8616873423258463</v>
+        <v>0.8456780910491943</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-120538</t>
+          <t>20250718-083054</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>45.77262568473816</v>
+        <v>52.27780103683472</v>
       </c>
       <c r="D5" t="n">
         <v>1.840000033378601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1460222074618706</v>
+        <v>0.1554264606685813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6458937525749207</v>
+        <v>0.7466422915458679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6458937525749207</v>
+        <v>0.7466422915458679</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6444025039672852</v>
+        <v>0.7464940547943115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.628936767578125</v>
+        <v>0.7171704769134521</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0621838569641113</v>
+        <v>0.0608980655670166</v>
       </c>
       <c r="K5" t="n">
-        <v>26.29045796394348</v>
+        <v>27.14522814750672</v>
       </c>
       <c r="L5" t="n">
-        <v>1.114406824111938</v>
+        <v>1.55985951423645</v>
       </c>
       <c r="M5" t="n">
-        <v>2.72886610031128</v>
+        <v>3.293828248977661</v>
       </c>
       <c r="N5" t="n">
-        <v>4.732161283493042</v>
+        <v>5.503634214401245</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1857344706853231</v>
+        <v>0.259976585706075</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4548110167185465</v>
+        <v>0.5489713748296102</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7886935472488403</v>
+        <v>0.917272369066874</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-120801</t>
+          <t>20250718-083325</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1849,53 +1849,53 @@
         <v>104</v>
       </c>
       <c r="C6" t="n">
-        <v>48.17028450965881</v>
+        <v>49.820885181427</v>
       </c>
       <c r="D6" t="n">
-        <v>1.840000033378601</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1499273639458876</v>
+        <v>0.1585315580551441</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6936519145965576</v>
+        <v>0.7232847213745117</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6936519145965576</v>
+        <v>0.7232847213745117</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6982021927833557</v>
+        <v>0.7287963628768921</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7050342559814453</v>
+        <v>0.730354368686676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0556862354278564</v>
+        <v>0.0652599334716796</v>
       </c>
       <c r="K6" t="n">
-        <v>20.9887900352478</v>
+        <v>26.96066570281982</v>
       </c>
       <c r="L6" t="n">
-        <v>1.466008186340332</v>
+        <v>1.291517972946167</v>
       </c>
       <c r="M6" t="n">
-        <v>2.732394456863404</v>
+        <v>2.944243669509888</v>
       </c>
       <c r="N6" t="n">
-        <v>5.210611343383789</v>
+        <v>5.067152738571167</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2443346977233886</v>
+        <v>0.2152529954910278</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4553990761439005</v>
+        <v>0.4907072782516479</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8684352238972982</v>
+        <v>0.8445254564285278</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-121022</t>
+          <t>20250718-083557</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C2" t="n">
-        <v>42.05907940864563</v>
+        <v>45.41528177261353</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1257521097476665</v>
+        <v>0.131141085143483</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7011010646820068</v>
+        <v>0.6267229318618774</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7011010646820068</v>
+        <v>0.6267229318618774</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7013482451438904</v>
+        <v>0.6278423070907593</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6782084703445435</v>
+        <v>0.6444714069366455</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0557973384857177</v>
+        <v>0.0538163185119628</v>
       </c>
       <c r="K2" t="n">
-        <v>23.62125396728516</v>
+        <v>24.0002429485321</v>
       </c>
       <c r="L2" t="n">
-        <v>1.310632467269898</v>
+        <v>1.411348819732666</v>
       </c>
       <c r="M2" t="n">
-        <v>2.936827421188354</v>
+        <v>2.933098793029785</v>
       </c>
       <c r="N2" t="n">
-        <v>6.213147163391113</v>
+        <v>7.005861520767212</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2184387445449829</v>
+        <v>0.2352248032887776</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4894712368647257</v>
+        <v>0.4888497988382975</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.035524527231853</v>
+        <v>1.167643586794535</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-150550</t>
+          <t>20250718-143434</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2257,53 +2257,53 @@
         <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>43.78855204582214</v>
+        <v>45.74247097969055</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1234137640086882</v>
+        <v>0.1328303529581892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6230510473251343</v>
+        <v>0.6839286088943481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6230510473251343</v>
+        <v>0.6839286088943481</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6201386451721191</v>
+        <v>0.6878553628921509</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5629271864891052</v>
+        <v>0.6414439678192139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0769798755645752</v>
+        <v>0.0541639328002929</v>
       </c>
       <c r="K3" t="n">
-        <v>23.48431324958801</v>
+        <v>23.79087781906128</v>
       </c>
       <c r="L3" t="n">
-        <v>1.446744680404663</v>
+        <v>1.374534368515015</v>
       </c>
       <c r="M3" t="n">
-        <v>2.817659378051758</v>
+        <v>2.931336164474488</v>
       </c>
       <c r="N3" t="n">
-        <v>6.201195955276489</v>
+        <v>6.593716144561768</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2411241134007772</v>
+        <v>0.2290890614191691</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4696098963419596</v>
+        <v>0.4885560274124145</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.033532659212749</v>
+        <v>1.098952690760295</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-150806</t>
+          <t>20250718-143657</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C4" t="n">
-        <v>43.37857055664063</v>
+        <v>43.03850173950195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1218963041218048</v>
+        <v>0.1294191021185654</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6319721937179565</v>
+        <v>0.68895024061203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6319721937179565</v>
+        <v>0.68895024061203</v>
       </c>
       <c r="H4" t="n">
-        <v>0.636763870716095</v>
+        <v>0.6934135556221008</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6285833120346069</v>
+        <v>0.734724760055542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0546588897705078</v>
+        <v>0.0554771423339843</v>
       </c>
       <c r="K4" t="n">
-        <v>23.73069453239441</v>
+        <v>24.00536799430847</v>
       </c>
       <c r="L4" t="n">
-        <v>1.341750621795654</v>
+        <v>1.046627998352051</v>
       </c>
       <c r="M4" t="n">
-        <v>2.880048990249634</v>
+        <v>2.976641654968262</v>
       </c>
       <c r="N4" t="n">
-        <v>6.321275949478149</v>
+        <v>6.533101320266724</v>
       </c>
       <c r="O4" t="n">
-        <v>0.223625103632609</v>
+        <v>0.1744379997253418</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4800081650416056</v>
+        <v>0.4961069424947102</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.053545991579692</v>
+        <v>1.088850220044454</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-151023</t>
+          <t>20250718-143919</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2499,53 +2499,53 @@
         <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>45.06064963340759</v>
+        <v>46.25395202636719</v>
       </c>
       <c r="D5" t="n">
         <v>0.8700000047683716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1272852086184317</v>
+        <v>0.127034586772584</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6206597089767456</v>
+        <v>0.6671746969223022</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6206597089767456</v>
+        <v>0.6671746969223022</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6214568018913269</v>
+        <v>0.6690571308135986</v>
       </c>
       <c r="I5" t="n">
-        <v>0.626645028591156</v>
+        <v>0.6029891967773438</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0523445606231689</v>
+        <v>0.048140525817871</v>
       </c>
       <c r="K5" t="n">
-        <v>23.21232986450196</v>
+        <v>24.11871910095215</v>
       </c>
       <c r="L5" t="n">
-        <v>1.30588436126709</v>
+        <v>1.396563291549683</v>
       </c>
       <c r="M5" t="n">
-        <v>2.888927221298218</v>
+        <v>2.972840309143066</v>
       </c>
       <c r="N5" t="n">
-        <v>6.247097492218018</v>
+        <v>6.551306486129761</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2176473935445149</v>
+        <v>0.2327605485916137</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4814878702163696</v>
+        <v>0.4954733848571777</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.04118291536967</v>
+        <v>1.09188441435496</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-151241</t>
+          <t>20250718-144138</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>41.25097680091858</v>
+        <v>49.86771368980408</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1246061646021329</v>
+        <v>0.1313126167329419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6129317283630371</v>
+        <v>0.7483503818511963</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6129317283630371</v>
+        <v>0.7483503818511963</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6157744526863098</v>
+        <v>0.7511734962463379</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5809199810028076</v>
+        <v>0.6390345692634583</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0524334907531738</v>
+        <v>0.06534576416015619</v>
       </c>
       <c r="K6" t="n">
-        <v>23.46203231811523</v>
+        <v>23.81100654602051</v>
       </c>
       <c r="L6" t="n">
-        <v>1.055818557739258</v>
+        <v>1.448276042938232</v>
       </c>
       <c r="M6" t="n">
-        <v>2.86266040802002</v>
+        <v>2.946967840194702</v>
       </c>
       <c r="N6" t="n">
-        <v>6.238085746765137</v>
+        <v>6.465084552764893</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1759697596232096</v>
+        <v>0.2413793404897054</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4771100680033366</v>
+        <v>0.491161306699117</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.03968095779419</v>
+        <v>1.077514092127482</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-151500</t>
+          <t>20250718-144401</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>72.67682671546936</v>
+        <v>78.6334331035614</v>
       </c>
       <c r="D2" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2909746104424153</v>
+        <v>0.296471729613187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6944183111190796</v>
+        <v>0.6994330883026123</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6944183111190796</v>
+        <v>0.6994330883026123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6959828734397888</v>
+        <v>0.7022585868835449</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6372686624526978</v>
+        <v>0.6752399802207947</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1023256778717041</v>
+        <v>0.1094872951507568</v>
       </c>
       <c r="K2" t="n">
-        <v>78.60752153396606</v>
+        <v>74.86317563056946</v>
       </c>
       <c r="L2" t="n">
-        <v>1.818894624710083</v>
+        <v>2.170860767364502</v>
       </c>
       <c r="M2" t="n">
-        <v>5.499219655990601</v>
+        <v>5.291807174682617</v>
       </c>
       <c r="N2" t="n">
-        <v>12.71187090873718</v>
+        <v>13.24315524101257</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3031491041183471</v>
+        <v>0.3618101278940837</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9165366093317668</v>
+        <v>0.8819678624471029</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.118645151456197</v>
+        <v>2.207192540168762</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-180700</t>
+          <t>20250718-202125</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>69.2372624874115</v>
+        <v>76.73153638839722</v>
       </c>
       <c r="D3" t="n">
         <v>6.480000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2886894987179683</v>
+        <v>0.2943025199990523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6945135593414307</v>
+        <v>0.7542868852615356</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6945135593414307</v>
+        <v>0.7542868852615356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6962993144989014</v>
+        <v>0.7568223476409912</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5982794165611267</v>
+        <v>0.3193633258342743</v>
       </c>
       <c r="J3" t="n">
-        <v>0.100950002670288</v>
+        <v>0.1056103706359863</v>
       </c>
       <c r="K3" t="n">
-        <v>71.87051153182983</v>
+        <v>75.06952428817749</v>
       </c>
       <c r="L3" t="n">
-        <v>2.106971979141236</v>
+        <v>2.174579858779907</v>
       </c>
       <c r="M3" t="n">
-        <v>5.163253545761108</v>
+        <v>5.869592666625977</v>
       </c>
       <c r="N3" t="n">
-        <v>12.72612571716309</v>
+        <v>13.39125847816467</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3511619965235392</v>
+        <v>0.3624299764633178</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8605422576268514</v>
+        <v>0.9782654444376628</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.121020952860514</v>
+        <v>2.231876413027445</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-181119</t>
+          <t>20250718-202556</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C4" t="n">
-        <v>68.09309434890747</v>
+        <v>74.33053302764893</v>
       </c>
       <c r="D4" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2927183600572439</v>
+        <v>0.2969598157690206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6986692547798157</v>
+        <v>0.7016305923461914</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6986692547798157</v>
+        <v>0.7016305923461914</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6968228816986084</v>
+        <v>0.7042144536972046</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6108111143112183</v>
+        <v>0.5678380727767944</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1033222675323486</v>
+        <v>0.1074450016021728</v>
       </c>
       <c r="K4" t="n">
-        <v>78.79468321800232</v>
+        <v>81.5532557964325</v>
       </c>
       <c r="L4" t="n">
-        <v>2.142669677734375</v>
+        <v>2.186485290527344</v>
       </c>
       <c r="M4" t="n">
-        <v>5.44807505607605</v>
+        <v>5.641492605209351</v>
       </c>
       <c r="N4" t="n">
-        <v>12.32638025283814</v>
+        <v>13.1341598033905</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3571116129557292</v>
+        <v>0.3644142150878906</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9080125093460084</v>
+        <v>0.9402487675348916</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.054396708806356</v>
+        <v>2.189026633898417</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-181534</t>
+          <t>20250718-203020</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>70.40203547477722</v>
+        <v>70.88654923439026</v>
       </c>
       <c r="D5" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2901538030816874</v>
+        <v>0.2945096492767334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6880099773406982</v>
+        <v>0.7243276834487915</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6880099773406982</v>
+        <v>0.7243276834487915</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6912660598754883</v>
+        <v>0.7237601280212402</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5666120052337646</v>
+        <v>0.6212132573127747</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1151294708251953</v>
+        <v>0.1059508323669433</v>
       </c>
       <c r="K5" t="n">
-        <v>78.70157957077026</v>
+        <v>75.07425951957703</v>
       </c>
       <c r="L5" t="n">
-        <v>1.88739824295044</v>
+        <v>2.195559978485107</v>
       </c>
       <c r="M5" t="n">
-        <v>5.514341115951538</v>
+        <v>5.336035013198853</v>
       </c>
       <c r="N5" t="n">
-        <v>12.59559488296509</v>
+        <v>13.08971524238586</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145663738250732</v>
+        <v>0.3659266630808512</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9190568526585896</v>
+        <v>0.8893391688664755</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.099265813827514</v>
+        <v>2.181619207064311</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-181949</t>
+          <t>20250718-203448</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>69.99614691734314</v>
+        <v>74.88798022270203</v>
       </c>
       <c r="D6" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2938378292780656</v>
+        <v>0.2938411738894401</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6302750706672668</v>
+        <v>0.6376839876174927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6302750706672668</v>
+        <v>0.6376839876174927</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6313826441764832</v>
+        <v>0.6390697956085205</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6229656338691711</v>
+        <v>0.6157055497169495</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1108949184417724</v>
+        <v>0.0944783687591552</v>
       </c>
       <c r="K6" t="n">
-        <v>72.84883427619934</v>
+        <v>74.98932862281799</v>
       </c>
       <c r="L6" t="n">
-        <v>1.888657569885254</v>
+        <v>2.141307830810547</v>
       </c>
       <c r="M6" t="n">
-        <v>5.695214509963989</v>
+        <v>5.339681386947632</v>
       </c>
       <c r="N6" t="n">
-        <v>12.73361277580261</v>
+        <v>13.47277593612671</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3147762616475423</v>
+        <v>0.3568846384684245</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9492024183273317</v>
+        <v>0.8899468978246053</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.122268795967102</v>
+        <v>2.245462656021118</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-182407</t>
+          <t>20250718-203911</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>64.27830123901367</v>
+        <v>63.26079678535461</v>
       </c>
       <c r="D2" t="n">
-        <v>5.670000076293945</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.162798645299509</v>
+        <v>0.1637446146744948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6111888885498047</v>
+        <v>0.6021657586097717</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6111888885498047</v>
+        <v>0.6021657586097717</v>
       </c>
       <c r="H2" t="n">
-        <v>0.613233208656311</v>
+        <v>0.6030622720718384</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6113539338111877</v>
+        <v>0.5793560743331909</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0657415390014648</v>
+        <v>0.0654335021972656</v>
       </c>
       <c r="K2" t="n">
-        <v>28.31322574615479</v>
+        <v>28.89270401000977</v>
       </c>
       <c r="L2" t="n">
-        <v>1.561763286590576</v>
+        <v>1.675353050231934</v>
       </c>
       <c r="M2" t="n">
-        <v>2.945440530776977</v>
+        <v>3.402865886688232</v>
       </c>
       <c r="N2" t="n">
-        <v>6.015262365341187</v>
+        <v>6.037841558456421</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2602938810984294</v>
+        <v>0.2792255083719889</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4909067551294963</v>
+        <v>0.5671443144480387</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.002543727556864</v>
+        <v>1.006306926409404</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-044437</t>
+          <t>20250719-130717</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>65.241370677948</v>
+        <v>64.45986437797546</v>
       </c>
       <c r="D3" t="n">
         <v>5.670000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1620148064797384</v>
+        <v>0.1640304349935971</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6044873595237732</v>
+        <v>0.607353687286377</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6044873595237732</v>
+        <v>0.607353687286377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6021729707717896</v>
+        <v>0.6061220169067383</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5769258141517639</v>
+        <v>0.5966941118240356</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0640127658843994</v>
+        <v>0.06619572639465331</v>
       </c>
       <c r="K3" t="n">
-        <v>27.88762354850769</v>
+        <v>28.85757541656494</v>
       </c>
       <c r="L3" t="n">
-        <v>1.609814167022705</v>
+        <v>1.678111553192139</v>
       </c>
       <c r="M3" t="n">
-        <v>2.917312383651733</v>
+        <v>3.096876859664917</v>
       </c>
       <c r="N3" t="n">
-        <v>5.947963237762451</v>
+        <v>6.315009355545044</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2683023611704508</v>
+        <v>0.2796852588653564</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4862187306086222</v>
+        <v>0.5161461432774862</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9913272062937418</v>
+        <v>1.052501559257507</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-044718</t>
+          <t>20250719-131000</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="C4" t="n">
-        <v>78.17797064781189</v>
+        <v>63.34784054756165</v>
       </c>
       <c r="D4" t="n">
-        <v>5.730000019073486</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1635246414074794</v>
+        <v>0.1637373612477229</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6082569360733032</v>
+        <v>0.6023575067520142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6082569360733032</v>
+        <v>0.6023575067520142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6064720153808594</v>
+        <v>0.6032167077064514</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5363224148750305</v>
+        <v>0.6009799838066101</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06487250328063961</v>
+        <v>0.0633418560028076</v>
       </c>
       <c r="K4" t="n">
-        <v>27.87039470672608</v>
+        <v>28.13618898391724</v>
       </c>
       <c r="L4" t="n">
-        <v>1.564545631408691</v>
+        <v>1.651325702667236</v>
       </c>
       <c r="M4" t="n">
-        <v>2.956007480621338</v>
+        <v>3.086149930953979</v>
       </c>
       <c r="N4" t="n">
-        <v>5.669780731201172</v>
+        <v>6.332332372665405</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2607576052347819</v>
+        <v>0.2752209504445393</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4926679134368896</v>
+        <v>0.5143583218256632</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9449634552001952</v>
+        <v>1.055388728777568</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-044959</t>
+          <t>20250719-131244</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>63.40711498260498</v>
+        <v>63.18796515464783</v>
       </c>
       <c r="D5" t="n">
-        <v>5.730000019073486</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1621308917299323</v>
+        <v>0.1631972537590907</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5974128246307373</v>
+        <v>0.6067825555801392</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5974128246307373</v>
+        <v>0.6067825555801392</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5986270904541016</v>
+        <v>0.6072930097579956</v>
       </c>
       <c r="I5" t="n">
-        <v>0.531217098236084</v>
+        <v>0.5808786153793335</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06649398803710931</v>
+        <v>0.064166784286499</v>
       </c>
       <c r="K5" t="n">
-        <v>27.80285596847535</v>
+        <v>22.9380738735199</v>
       </c>
       <c r="L5" t="n">
-        <v>1.628441572189331</v>
+        <v>1.687938451766968</v>
       </c>
       <c r="M5" t="n">
-        <v>3.007652997970581</v>
+        <v>3.119208335876465</v>
       </c>
       <c r="N5" t="n">
-        <v>5.933817625045776</v>
+        <v>5.853946447372437</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2714069286982218</v>
+        <v>0.2813230752944946</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5012754996617635</v>
+        <v>0.5198680559794108</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.988969604174296</v>
+        <v>0.9756577412287394</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-045254</t>
+          <t>20250719-131526</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>61.2966411113739</v>
+        <v>69.11628746986389</v>
       </c>
       <c r="D6" t="n">
-        <v>5.730000019073486</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.165768190072133</v>
+        <v>0.1632873886509945</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6106985807418823</v>
+        <v>0.6021234393119812</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6106985807418823</v>
+        <v>0.6021234393119812</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6116484403610229</v>
+        <v>0.6043533086776733</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6048852801322937</v>
+        <v>0.5893096327781677</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0650200843811035</v>
+        <v>0.0661025047302246</v>
       </c>
       <c r="K6" t="n">
-        <v>22.30660653114319</v>
+        <v>28.6200053691864</v>
       </c>
       <c r="L6" t="n">
-        <v>1.614780426025391</v>
+        <v>1.602016925811768</v>
       </c>
       <c r="M6" t="n">
-        <v>3.773744106292725</v>
+        <v>3.028592586517334</v>
       </c>
       <c r="N6" t="n">
-        <v>5.664159774780273</v>
+        <v>6.294787168502808</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2691300710042317</v>
+        <v>0.2670028209686279</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6289573510487875</v>
+        <v>0.5047654310862223</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9440266291300456</v>
+        <v>1.049131194750468</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-045534</t>
+          <t>20250719-131808</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>46.12351202964783</v>
+        <v>46.9076361656189</v>
       </c>
       <c r="D2" t="n">
-        <v>3.450000047683716</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1026775962428042</v>
+        <v>0.1025969500725085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6142635345458984</v>
+        <v>0.6103848814964294</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6142635345458984</v>
+        <v>0.6103848814964294</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6141370534896851</v>
+        <v>0.6105414032936096</v>
       </c>
       <c r="I2" t="n">
-        <v>0.609071671962738</v>
+        <v>0.6151244640350342</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0505650043487548</v>
+        <v>0.0412719249725341</v>
       </c>
       <c r="K2" t="n">
-        <v>17.8224766254425</v>
+        <v>18.02299404144287</v>
       </c>
       <c r="L2" t="n">
-        <v>1.054044723510742</v>
+        <v>1.061752080917358</v>
       </c>
       <c r="M2" t="n">
-        <v>2.005423784255981</v>
+        <v>2.033459901809692</v>
       </c>
       <c r="N2" t="n">
-        <v>3.301454067230225</v>
+        <v>3.46581244468689</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1756741205851237</v>
+        <v>0.176958680152893</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3342372973759969</v>
+        <v>0.3389099836349487</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5502423445383707</v>
+        <v>0.5776354074478149</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-074623</t>
+          <t>20250719-193810</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C3" t="n">
-        <v>53.25854849815369</v>
+        <v>54.55430269241333</v>
       </c>
       <c r="D3" t="n">
-        <v>3.440000057220459</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1016383318938025</v>
+        <v>0.1040061289264309</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6128360033035278</v>
+        <v>0.5965043306350708</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6128360033035278</v>
+        <v>0.5965043306350708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6125539541244507</v>
+        <v>0.5969869494438171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4975179433822632</v>
+        <v>0.5985857248306274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0484118461608886</v>
+        <v>0.0436048507690429</v>
       </c>
       <c r="K3" t="n">
-        <v>17.99784374237061</v>
+        <v>18.21030855178833</v>
       </c>
       <c r="L3" t="n">
-        <v>1.041134119033814</v>
+        <v>1.124585390090942</v>
       </c>
       <c r="M3" t="n">
-        <v>1.981528520584106</v>
+        <v>2.436961650848389</v>
       </c>
       <c r="N3" t="n">
-        <v>3.297221183776855</v>
+        <v>3.434296607971191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1735223531723022</v>
+        <v>0.1874308983484904</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3302547534306844</v>
+        <v>0.4061602751413981</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5495368639628092</v>
+        <v>0.5723827679951986</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-074824</t>
+          <t>20250719-194012</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4691,53 +4691,53 @@
         <v>104</v>
       </c>
       <c r="C4" t="n">
-        <v>42.50151228904724</v>
+        <v>45.530118227005</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.101931672829848</v>
+        <v>0.103894653228613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.509099543094635</v>
+        <v>0.6085318326950073</v>
       </c>
       <c r="G4" t="n">
-        <v>0.509099543094635</v>
+        <v>0.6085318326950073</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5006903409957886</v>
+        <v>0.6074460744857788</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4736853837966919</v>
+        <v>0.6042457818984985</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0404577255249023</v>
+        <v>0.0426352024078369</v>
       </c>
       <c r="K4" t="n">
-        <v>12.52057361602783</v>
+        <v>18.3168158531189</v>
       </c>
       <c r="L4" t="n">
-        <v>1.018126964569092</v>
+        <v>1.131932258605957</v>
       </c>
       <c r="M4" t="n">
-        <v>2.361378908157349</v>
+        <v>2.424085378646851</v>
       </c>
       <c r="N4" t="n">
-        <v>3.350840330123901</v>
+        <v>3.492770671844482</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1696878274281819</v>
+        <v>0.1886553764343261</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3935631513595581</v>
+        <v>0.4040142297744751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5584733883539835</v>
+        <v>0.5821284453074137</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-075031</t>
+          <t>20250719-194222</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4812,53 +4812,53 @@
         <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60293865203857</v>
+        <v>47.91543698310852</v>
       </c>
       <c r="D5" t="n">
-        <v>3.369999885559082</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1036157057835505</v>
+        <v>0.1055380083047426</v>
       </c>
       <c r="F5" t="n">
-        <v>0.617135763168335</v>
+        <v>0.6126317977905273</v>
       </c>
       <c r="G5" t="n">
-        <v>0.617135763168335</v>
+        <v>0.6126317977905273</v>
       </c>
       <c r="H5" t="n">
-        <v>0.616864025592804</v>
+        <v>0.6111290454864502</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6160593032836914</v>
+        <v>0.33187997341156</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0411093235015869</v>
+        <v>0.0411770343780517</v>
       </c>
       <c r="K5" t="n">
-        <v>17.92897701263428</v>
+        <v>18.04408478736877</v>
       </c>
       <c r="L5" t="n">
-        <v>1.03819727897644</v>
+        <v>1.099365472793579</v>
       </c>
       <c r="M5" t="n">
-        <v>2.252296686172485</v>
+        <v>2.029290914535522</v>
       </c>
       <c r="N5" t="n">
-        <v>3.310301780700684</v>
+        <v>3.470319032669067</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1730328798294067</v>
+        <v>0.1832275787989298</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3753827810287475</v>
+        <v>0.3382151524225871</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5517169634501139</v>
+        <v>0.5783865054448446</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-075223</t>
+          <t>20250719-194424</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>42.86307454109192</v>
+        <v>48.34620404243469</v>
       </c>
       <c r="D6" t="n">
-        <v>3.339999914169312</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1022952863803276</v>
+        <v>0.1041637407530338</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6002219915390015</v>
+        <v>0.5979527831077576</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6002219915390015</v>
+        <v>0.5979527831077576</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5977780818939209</v>
+        <v>0.5970353484153748</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5977439880371094</v>
+        <v>0.6014353632926941</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0435912609100341</v>
+        <v>0.041935920715332</v>
       </c>
       <c r="K6" t="n">
-        <v>18.01203060150146</v>
+        <v>12.88816380500794</v>
       </c>
       <c r="L6" t="n">
-        <v>1.025813341140747</v>
+        <v>1.061025857925415</v>
       </c>
       <c r="M6" t="n">
-        <v>2.254430532455444</v>
+        <v>2.067927598953247</v>
       </c>
       <c r="N6" t="n">
-        <v>3.360158443450928</v>
+        <v>3.424293041229248</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1709688901901245</v>
+        <v>0.1768376429875691</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3757384220759074</v>
+        <v>0.3446545998255412</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5600264072418213</v>
+        <v>0.5707155068715414</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-075419</t>
+          <t>20250719-194628</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>38.87993812561035</v>
+        <v>47.55352854728699</v>
       </c>
       <c r="D2" t="n">
-        <v>2.200000047683716</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1032636073919442</v>
+        <v>0.104133992425857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4256009459495544</v>
+        <v>0.6179323196411133</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4256009459495544</v>
+        <v>0.6179323196411133</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4286283850669861</v>
+        <v>0.6213950514793396</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4067323803901672</v>
+        <v>0.6160985231399536</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0428884029388427</v>
+        <v>0.0379393100738525</v>
       </c>
       <c r="K2" t="n">
-        <v>17.64823341369629</v>
+        <v>17.9989812374115</v>
       </c>
       <c r="L2" t="n">
-        <v>0.956507921218872</v>
+        <v>0.961467981338501</v>
       </c>
       <c r="M2" t="n">
-        <v>1.938477039337158</v>
+        <v>2.05432391166687</v>
       </c>
       <c r="N2" t="n">
-        <v>3.630507707595825</v>
+        <v>3.712939262390137</v>
       </c>
       <c r="O2" t="n">
-        <v>0.159417986869812</v>
+        <v>0.1602446635564168</v>
       </c>
       <c r="P2" t="n">
-        <v>0.323079506556193</v>
+        <v>0.342387318611145</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6050846179326376</v>
+        <v>0.6188232103983561</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-095726</t>
+          <t>20250720-000113</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5341,53 +5341,53 @@
         <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>38.54562258720398</v>
+        <v>40.41632771492005</v>
       </c>
       <c r="D3" t="n">
-        <v>2.190000057220459</v>
+        <v>2.440000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1011261252256539</v>
+        <v>0.1059268781772026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3843465447425842</v>
+        <v>0.6137626171112061</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3843465447425842</v>
+        <v>0.6137626171112061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.378254771232605</v>
+        <v>0.6124452352523804</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3347766101360321</v>
+        <v>0.6178182363510132</v>
       </c>
       <c r="J3" t="n">
-        <v>0.037513256072998</v>
+        <v>0.0413196086883544</v>
       </c>
       <c r="K3" t="n">
-        <v>17.68930149078369</v>
+        <v>18.06377530097961</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9054136276245116</v>
+        <v>0.971670150756836</v>
       </c>
       <c r="M3" t="n">
-        <v>1.919690608978272</v>
+        <v>2.041831254959106</v>
       </c>
       <c r="N3" t="n">
-        <v>3.885154008865357</v>
+        <v>3.755629301071167</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1509022712707519</v>
+        <v>0.1619450251261393</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3199484348297119</v>
+        <v>0.3403052091598511</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6475256681442261</v>
+        <v>0.6259382168451945</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-095920</t>
+          <t>20250720-000316</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="n">
-        <v>38.57269072532654</v>
+        <v>46.29108881950378</v>
       </c>
       <c r="D4" t="n">
         <v>2.190000057220459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1031115674055539</v>
+        <v>0.1050979514275827</v>
       </c>
       <c r="F4" t="n">
-        <v>0.616713285446167</v>
+        <v>0.6040718555450439</v>
       </c>
       <c r="G4" t="n">
-        <v>0.616713285446167</v>
+        <v>0.6040718555450439</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6175572872161865</v>
+        <v>0.6022583842277527</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6170653104782104</v>
+        <v>0.5977650284767151</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0396404266357421</v>
+        <v>0.0411028861999511</v>
       </c>
       <c r="K4" t="n">
-        <v>17.60730004310608</v>
+        <v>17.90604543685913</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9189813137054444</v>
+        <v>1.01902961730957</v>
       </c>
       <c r="M4" t="n">
-        <v>1.982594013214112</v>
+        <v>2.344335556030273</v>
       </c>
       <c r="N4" t="n">
-        <v>3.918940305709839</v>
+        <v>4.080416202545166</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1531635522842407</v>
+        <v>0.169838269551595</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3304323355356852</v>
+        <v>0.3907225926717122</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6531567176183065</v>
+        <v>0.680069367090861</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-100113</t>
+          <t>20250720-000513</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>38.90462350845337</v>
+        <v>44.06217861175537</v>
       </c>
       <c r="D5" t="n">
         <v>2.230000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.102235374542383</v>
+        <v>0.1046937829569766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6065766215324402</v>
+        <v>0.6155451536178589</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6065766215324402</v>
+        <v>0.6155451536178589</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6050999164581299</v>
+        <v>0.6144675016403198</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5988750457763672</v>
+        <v>0.6112265586853027</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0415637493133544</v>
+        <v>0.0413377285003662</v>
       </c>
       <c r="K5" t="n">
-        <v>17.65484380722046</v>
+        <v>12.19975256919861</v>
       </c>
       <c r="L5" t="n">
-        <v>0.963853359222412</v>
+        <v>0.9769768714904784</v>
       </c>
       <c r="M5" t="n">
-        <v>1.968463897705078</v>
+        <v>1.99467921257019</v>
       </c>
       <c r="N5" t="n">
-        <v>3.612431526184082</v>
+        <v>3.787367582321167</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1606422265370687</v>
+        <v>0.1628294785817464</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3280773162841797</v>
+        <v>0.332446535428365</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6020719210306803</v>
+        <v>0.6312279303868612</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-100306</t>
+          <t>20250720-000716</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>38.8484148979187</v>
+        <v>45.21643090248108</v>
       </c>
       <c r="D6" t="n">
-        <v>2.210000038146973</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1029985959713275</v>
+        <v>0.104214924724162</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6112421751022339</v>
+        <v>0.6110843420028687</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6112421751022339</v>
+        <v>0.6110843420028687</v>
       </c>
       <c r="H6" t="n">
-        <v>0.610335648059845</v>
+        <v>0.6127482056617737</v>
       </c>
       <c r="I6" t="n">
-        <v>0.608333945274353</v>
+        <v>0.608864426612854</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0512511730194091</v>
+        <v>0.0440285205841064</v>
       </c>
       <c r="K6" t="n">
-        <v>17.17710375785828</v>
+        <v>17.77091097831726</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9561474323272704</v>
+        <v>0.9900259971618652</v>
       </c>
       <c r="M6" t="n">
-        <v>2.265530586242676</v>
+        <v>2.033800363540649</v>
       </c>
       <c r="N6" t="n">
-        <v>3.943901062011719</v>
+        <v>4.153174877166748</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1593579053878784</v>
+        <v>0.1650043328603108</v>
       </c>
       <c r="P6" t="n">
-        <v>0.377588431040446</v>
+        <v>0.3389667272567749</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6573168436686198</v>
+        <v>0.6921958128611246</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-100459</t>
+          <t>20250720-000916</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_cell_labels.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_cell_labels.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
-        <v>34.32987022399902</v>
+        <v>42.26731443405152</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6600000262260437</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.029522065932934</v>
+        <v>0.0298497232038582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.639243483543396</v>
+        <v>0.6440472602844238</v>
       </c>
       <c r="G2" t="n">
-        <v>0.639243483543396</v>
+        <v>0.6440472602844238</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6395139098167419</v>
+        <v>0.6450700163841248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6398996114730835</v>
+        <v>0.6324767470359802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0333278179168701</v>
+        <v>0.0292088985443115</v>
       </c>
       <c r="K2" t="n">
-        <v>17.3544340133667</v>
+        <v>17.36414003372192</v>
       </c>
       <c r="L2" t="n">
-        <v>0.968569040298462</v>
+        <v>1.029820442199707</v>
       </c>
       <c r="M2" t="n">
-        <v>2.431927442550659</v>
+        <v>2.425535917282104</v>
       </c>
       <c r="N2" t="n">
-        <v>3.069146156311035</v>
+        <v>3.084274768829346</v>
       </c>
       <c r="O2" t="n">
-        <v>0.161428173383077</v>
+        <v>0.1716367403666178</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4053212404251098</v>
+        <v>0.4042559862136841</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5115243593851725</v>
+        <v>0.514045794804891</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-044000</t>
+          <t>20250723-151856</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
-        <v>34.00672602653503</v>
+        <v>43.31702542304993</v>
       </c>
       <c r="D3" t="n">
         <v>0.7799999713897705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0298300935671879</v>
+        <v>0.0298351675486392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6566990613937378</v>
+        <v>0.6684951782226562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6566990613937378</v>
+        <v>0.6684951782226562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6574235558509827</v>
+        <v>0.6672556400299072</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6397659778594971</v>
+        <v>0.6629012227058411</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0321640968322753</v>
+        <v>0.0284802913665771</v>
       </c>
       <c r="K3" t="n">
-        <v>17.54133725166321</v>
+        <v>17.30543804168701</v>
       </c>
       <c r="L3" t="n">
-        <v>1.002272129058838</v>
+        <v>0.9680953025817872</v>
       </c>
       <c r="M3" t="n">
-        <v>2.373407602310181</v>
+        <v>2.436877965927124</v>
       </c>
       <c r="N3" t="n">
-        <v>3.055575370788574</v>
+        <v>3.072570562362671</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1670453548431396</v>
+        <v>0.1613492170969645</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3955679337183634</v>
+        <v>0.4061463276545207</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5092625617980957</v>
+        <v>0.5120950937271118</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-044146</t>
+          <t>20250723-152050</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="C4" t="n">
-        <v>36.24293303489685</v>
+        <v>47.86877202987671</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0290867341192144</v>
+        <v>0.0300292721042384</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6277965903282166</v>
+        <v>0.6728622913360596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6277965903282166</v>
+        <v>0.6728622913360596</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6266106963157654</v>
+        <v>0.6724125146865845</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6028972268104553</v>
+        <v>0.6682752966880798</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0406644344329834</v>
+        <v>0.0323212146759033</v>
       </c>
       <c r="K4" t="n">
-        <v>17.2536153793335</v>
+        <v>17.28427386283875</v>
       </c>
       <c r="L4" t="n">
-        <v>1.011214733123779</v>
+        <v>1.034707069396973</v>
       </c>
       <c r="M4" t="n">
-        <v>2.427031278610229</v>
+        <v>2.387131929397583</v>
       </c>
       <c r="N4" t="n">
-        <v>3.035638570785522</v>
+        <v>3.062593221664429</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1685357888539632</v>
+        <v>0.1724511782328287</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4045052131017049</v>
+        <v>0.3978553215662638</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.505939761797587</v>
+        <v>0.5104322036107382</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-044332</t>
+          <t>20250723-152246</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>34.44605755805969</v>
+        <v>39.24957489967346</v>
       </c>
       <c r="D5" t="n">
         <v>0.7799999713897705</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0298231152387765</v>
+        <v>0.0297246613810138</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6562966108322144</v>
+        <v>0.6441760063171387</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6562966108322144</v>
+        <v>0.6441760063171387</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6570454835891724</v>
+        <v>0.6450304985046387</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6467530727386475</v>
+        <v>0.637529194355011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0315554141998291</v>
+        <v>0.0332107543945312</v>
       </c>
       <c r="K5" t="n">
-        <v>17.35628247261047</v>
+        <v>17.33753204345703</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9945504665374756</v>
+        <v>1.025492668151856</v>
       </c>
       <c r="M5" t="n">
-        <v>2.411879777908325</v>
+        <v>2.391236066818237</v>
       </c>
       <c r="N5" t="n">
-        <v>3.048125028610229</v>
+        <v>3.067405462265014</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1657584110895792</v>
+        <v>0.1709154446919759</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4019799629847209</v>
+        <v>0.3985393444697062</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.508020838101705</v>
+        <v>0.5112342437108358</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-044521</t>
+          <t>20250723-152446</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="C6" t="n">
-        <v>33.71496987342834</v>
+        <v>42.2835750579834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0294001973592317</v>
+        <v>0.0291159050070124</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6564586758613586</v>
+        <v>0.6419366598129272</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6564586758613586</v>
+        <v>0.6419366598129272</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6576645970344543</v>
+        <v>0.6416496634483337</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6522453427314758</v>
+        <v>0.6360316872596741</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0326282978057861</v>
+        <v>0.0334019660949707</v>
       </c>
       <c r="K6" t="n">
-        <v>17.24863576889038</v>
+        <v>17.23364543914795</v>
       </c>
       <c r="L6" t="n">
-        <v>1.008092164993286</v>
+        <v>1.015296459197998</v>
       </c>
       <c r="M6" t="n">
-        <v>2.453896284103394</v>
+        <v>2.383548736572266</v>
       </c>
       <c r="N6" t="n">
-        <v>3.060220718383789</v>
+        <v>3.00025486946106</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1680153608322143</v>
+        <v>0.1692160765329996</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4089827140172322</v>
+        <v>0.3972581227620442</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5100367863972982</v>
+        <v>0.5000424782435099</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-044707</t>
+          <t>20250723-152637</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C2" t="n">
-        <v>55.41064095497131</v>
+        <v>61.40020394325256</v>
       </c>
       <c r="D2" t="n">
-        <v>1.840000033378601</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1568329093836936</v>
+        <v>0.1593295733133951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7415280938148499</v>
+        <v>0.7658626437187195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7415280938148499</v>
+        <v>0.7658626437187195</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7439950704574585</v>
+        <v>0.7697124481201172</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7357286810874939</v>
+        <v>0.7414498329162598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0621159076690673</v>
+        <v>0.0730960369110107</v>
       </c>
       <c r="K2" t="n">
-        <v>27.32370924949646</v>
+        <v>27.08937788009644</v>
       </c>
       <c r="L2" t="n">
-        <v>1.251915693283081</v>
+        <v>1.2483069896698</v>
       </c>
       <c r="M2" t="n">
-        <v>2.952176332473755</v>
+        <v>2.916579723358154</v>
       </c>
       <c r="N2" t="n">
-        <v>5.09554934501648</v>
+        <v>5.079947471618652</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2086526155471801</v>
+        <v>0.2080511649449666</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4920293887456258</v>
+        <v>0.4860966205596924</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8492582241694132</v>
+        <v>0.846657911936442</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-082550</t>
+          <t>20250721-135011</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C3" t="n">
-        <v>49.9752824306488</v>
+        <v>56.16123414039612</v>
       </c>
       <c r="D3" t="n">
-        <v>1.840000033378601</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E3" t="n">
-        <v>0.159157762160668</v>
+        <v>0.155260314864497</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7878544926643372</v>
+        <v>0.7551655769348145</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7878544926643372</v>
+        <v>0.7551655769348145</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7924606800079346</v>
+        <v>0.7586854100227356</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7743946313858032</v>
+        <v>0.7446950674057007</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0595805644989013</v>
+        <v>0.0669145584106445</v>
       </c>
       <c r="K3" t="n">
-        <v>27.28975605964661</v>
+        <v>27.33711576461792</v>
       </c>
       <c r="L3" t="n">
-        <v>1.228995561599731</v>
+        <v>1.307594537734985</v>
       </c>
       <c r="M3" t="n">
-        <v>2.977825403213501</v>
+        <v>2.920489072799683</v>
       </c>
       <c r="N3" t="n">
-        <v>5.015619039535522</v>
+        <v>5.009329795837402</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2048325935999552</v>
+        <v>0.2179324229558309</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4963042338689168</v>
+        <v>0.4867481787999471</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8359365065892538</v>
+        <v>0.8348882993062338</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-082825</t>
+          <t>20250721-135252</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C4" t="n">
-        <v>50.67975687980652</v>
+        <v>72.79786920547485</v>
       </c>
       <c r="D4" t="n">
-        <v>1.840000033378601</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1565438673036907</v>
+        <v>0.1557247275259436</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7277190089225769</v>
+        <v>0.7296647429466248</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7277190089225769</v>
+        <v>0.7296647429466248</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7314742803573608</v>
+        <v>0.7394026517868042</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7319223880767822</v>
+        <v>0.7355801463127136</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0654671192169189</v>
+        <v>0.0568373203277587</v>
       </c>
       <c r="K4" t="n">
-        <v>26.8362774848938</v>
+        <v>27.13047552108765</v>
       </c>
       <c r="L4" t="n">
-        <v>1.330915212631226</v>
+        <v>1.517706155776978</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95327091217041</v>
+        <v>3.229800462722778</v>
       </c>
       <c r="N4" t="n">
-        <v>5.074068546295166</v>
+        <v>5.47118067741394</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2218192021052042</v>
+        <v>0.2529510259628296</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4922118186950683</v>
+        <v>0.538300077120463</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8456780910491943</v>
+        <v>0.9118634462356568</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-083054</t>
+          <t>20250721-135528</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C5" t="n">
-        <v>52.27780103683472</v>
+        <v>66.62091994285583</v>
       </c>
       <c r="D5" t="n">
         <v>1.840000033378601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1554264606685813</v>
+        <v>0.1570059458414713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7466422915458679</v>
+        <v>0.7498704195022583</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7466422915458679</v>
+        <v>0.7498704195022583</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7464940547943115</v>
+        <v>0.7533116340637207</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7171704769134521</v>
+        <v>0.748577356338501</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0608980655670166</v>
+        <v>0.0646383762359619</v>
       </c>
       <c r="K5" t="n">
-        <v>27.14522814750672</v>
+        <v>27.22355222702026</v>
       </c>
       <c r="L5" t="n">
-        <v>1.55985951423645</v>
+        <v>1.215047121047974</v>
       </c>
       <c r="M5" t="n">
-        <v>3.293828248977661</v>
+        <v>2.940049171447754</v>
       </c>
       <c r="N5" t="n">
-        <v>5.503634214401245</v>
+        <v>5.089726448059082</v>
       </c>
       <c r="O5" t="n">
-        <v>0.259976585706075</v>
+        <v>0.2025078535079956</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5489713748296102</v>
+        <v>0.4900081952412923</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.917272369066874</v>
+        <v>0.8482877413431803</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-083325</t>
+          <t>20250721-135821</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
-        <v>49.820885181427</v>
+        <v>61.23716640472412</v>
       </c>
       <c r="D6" t="n">
-        <v>1.960000038146973</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1585315580551441</v>
+        <v>0.1575978318257117</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7232847213745117</v>
+        <v>0.7601711750030518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7232847213745117</v>
+        <v>0.7601711750030518</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7287963628768921</v>
+        <v>0.7599652409553528</v>
       </c>
       <c r="I6" t="n">
-        <v>0.730354368686676</v>
+        <v>0.7574892640113831</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0652599334716796</v>
+        <v>0.06286478042602529</v>
       </c>
       <c r="K6" t="n">
-        <v>26.96066570281982</v>
+        <v>27.01767873764038</v>
       </c>
       <c r="L6" t="n">
-        <v>1.291517972946167</v>
+        <v>1.522054195404053</v>
       </c>
       <c r="M6" t="n">
-        <v>2.944243669509888</v>
+        <v>3.264047384262085</v>
       </c>
       <c r="N6" t="n">
-        <v>5.067152738571167</v>
+        <v>5.439741134643555</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2152529954910278</v>
+        <v>0.2536756992340088</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4907072782516479</v>
+        <v>0.5440078973770142</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8445254564285278</v>
+        <v>0.9066235224405924</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-083557</t>
+          <t>20250721-140107</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>45.41528177261353</v>
+        <v>60.71373438835144</v>
       </c>
       <c r="D2" t="n">
         <v>0.8700000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.131141085143483</v>
+        <v>0.1320147914374434</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6267229318618774</v>
+        <v>0.6933457255363464</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6267229318618774</v>
+        <v>0.6933457255363464</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6278423070907593</v>
+        <v>0.6943120360374451</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6444714069366455</v>
+        <v>0.6363945007324219</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0538163185119628</v>
+        <v>0.0556206703186035</v>
       </c>
       <c r="K2" t="n">
-        <v>24.0002429485321</v>
+        <v>24.09565901756286</v>
       </c>
       <c r="L2" t="n">
-        <v>1.411348819732666</v>
+        <v>1.125351428985596</v>
       </c>
       <c r="M2" t="n">
-        <v>2.933098793029785</v>
+        <v>3.369800090789795</v>
       </c>
       <c r="N2" t="n">
-        <v>7.005861520767212</v>
+        <v>6.938465118408203</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2352248032887776</v>
+        <v>0.1875585714975992</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4888497988382975</v>
+        <v>0.5616333484649658</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.167643586794535</v>
+        <v>1.156410853068034</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-143434</t>
+          <t>20250721-203842</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="C3" t="n">
-        <v>45.74247097969055</v>
+        <v>65.03590297698975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.9100000262260436</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1328303529581892</v>
+        <v>0.1319007393699021</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6839286088943481</v>
+        <v>0.700688362121582</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6839286088943481</v>
+        <v>0.700688362121582</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6878553628921509</v>
+        <v>0.706447958946228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6414439678192139</v>
+        <v>0.6670752763748169</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0541639328002929</v>
+        <v>0.0521423816680908</v>
       </c>
       <c r="K3" t="n">
-        <v>23.79087781906128</v>
+        <v>24.26591825485229</v>
       </c>
       <c r="L3" t="n">
-        <v>1.374534368515015</v>
+        <v>1.064702033996582</v>
       </c>
       <c r="M3" t="n">
-        <v>2.931336164474488</v>
+        <v>3.032310009002685</v>
       </c>
       <c r="N3" t="n">
-        <v>6.593716144561768</v>
+        <v>6.875733375549316</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2290890614191691</v>
+        <v>0.1774503389994303</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4885560274124145</v>
+        <v>0.5053850015004476</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.098952690760295</v>
+        <v>1.145955562591553</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-143657</t>
+          <t>20250721-204119</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C4" t="n">
-        <v>43.03850173950195</v>
+        <v>58.87224221229553</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.9100000262260436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1294191021185654</v>
+        <v>0.1291392925712796</v>
       </c>
       <c r="F4" t="n">
-        <v>0.68895024061203</v>
+        <v>0.7029737234115601</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68895024061203</v>
+        <v>0.7029737234115601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6934135556221008</v>
+        <v>0.7028905749320984</v>
       </c>
       <c r="I4" t="n">
-        <v>0.734724760055542</v>
+        <v>0.5725107192993164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0554771423339843</v>
+        <v>0.0516083240509033</v>
       </c>
       <c r="K4" t="n">
-        <v>24.00536799430847</v>
+        <v>24.38143372535706</v>
       </c>
       <c r="L4" t="n">
-        <v>1.046627998352051</v>
+        <v>1.099071264266968</v>
       </c>
       <c r="M4" t="n">
-        <v>2.976641654968262</v>
+        <v>2.989849328994751</v>
       </c>
       <c r="N4" t="n">
-        <v>6.533101320266724</v>
+        <v>6.873994588851929</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1744379997253418</v>
+        <v>0.1831785440444946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4961069424947102</v>
+        <v>0.4983082214991252</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.088850220044454</v>
+        <v>1.145665764808655</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-143919</t>
+          <t>20250721-204401</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="C5" t="n">
-        <v>46.25395202636719</v>
+        <v>70.22658729553223</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="E5" t="n">
-        <v>0.127034586772584</v>
+        <v>0.1284600647016503</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6671746969223022</v>
+        <v>0.7500448226928711</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6671746969223022</v>
+        <v>0.7500448226928711</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6690571308135986</v>
+        <v>0.7569848895072937</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6029891967773438</v>
+        <v>0.6022428870201111</v>
       </c>
       <c r="J5" t="n">
-        <v>0.048140525817871</v>
+        <v>0.055178165435791</v>
       </c>
       <c r="K5" t="n">
-        <v>24.11871910095215</v>
+        <v>24.1863009929657</v>
       </c>
       <c r="L5" t="n">
-        <v>1.396563291549683</v>
+        <v>1.407586336135864</v>
       </c>
       <c r="M5" t="n">
-        <v>2.972840309143066</v>
+        <v>3.030851364135742</v>
       </c>
       <c r="N5" t="n">
-        <v>6.551306486129761</v>
+        <v>6.486614465713501</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2327605485916137</v>
+        <v>0.2345977226893107</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4954733848571777</v>
+        <v>0.5051418940226237</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.09188441435496</v>
+        <v>1.08110241095225</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-144138</t>
+          <t>20250721-204637</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>49.86771368980408</v>
+        <v>60.16301584243774</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.9100000262260436</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1313126167329419</v>
+        <v>0.1289501126180558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7483503818511963</v>
+        <v>0.6919240355491638</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7483503818511963</v>
+        <v>0.6919240355491638</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7511734962463379</v>
+        <v>0.6970463991165161</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6390345692634583</v>
+        <v>0.6257520914077759</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06534576416015619</v>
+        <v>0.0566194057464599</v>
       </c>
       <c r="K6" t="n">
-        <v>23.81100654602051</v>
+        <v>18.4786057472229</v>
       </c>
       <c r="L6" t="n">
-        <v>1.448276042938232</v>
+        <v>1.109384536743164</v>
       </c>
       <c r="M6" t="n">
-        <v>2.946967840194702</v>
+        <v>2.969098091125488</v>
       </c>
       <c r="N6" t="n">
-        <v>6.465084552764893</v>
+        <v>6.520265340805054</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2413793404897054</v>
+        <v>0.1848974227905273</v>
       </c>
       <c r="P6" t="n">
-        <v>0.491161306699117</v>
+        <v>0.494849681854248</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.077514092127482</v>
+        <v>1.086710890134176</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-144401</t>
+          <t>20250721-204924</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C2" t="n">
-        <v>78.6334331035614</v>
+        <v>86.42114114761353</v>
       </c>
       <c r="D2" t="n">
         <v>6.440000057220459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.296471729613187</v>
+        <v>0.2971796231676442</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6994330883026123</v>
+        <v>0.6559324264526367</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6994330883026123</v>
+        <v>0.6559324264526367</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7022585868835449</v>
+        <v>0.6542590856552124</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6752399802207947</v>
+        <v>0.6182125806808472</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1094872951507568</v>
+        <v>0.1088130474090576</v>
       </c>
       <c r="K2" t="n">
-        <v>74.86317563056946</v>
+        <v>74.75201511383057</v>
       </c>
       <c r="L2" t="n">
-        <v>2.170860767364502</v>
+        <v>2.231655597686768</v>
       </c>
       <c r="M2" t="n">
-        <v>5.291807174682617</v>
+        <v>5.309502840042114</v>
       </c>
       <c r="N2" t="n">
-        <v>13.24315524101257</v>
+        <v>13.23191142082214</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3618101278940837</v>
+        <v>0.3719425996144612</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8819678624471029</v>
+        <v>0.884917140007019</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.207192540168762</v>
+        <v>2.205318570137024</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-202125</t>
+          <t>20250722-030823</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="C3" t="n">
-        <v>76.73153638839722</v>
+        <v>95.6386580467224</v>
       </c>
       <c r="D3" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2943025199990523</v>
+        <v>0.2970479412211312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7542868852615356</v>
+        <v>0.7010635137557983</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7542868852615356</v>
+        <v>0.7010635137557983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7568223476409912</v>
+        <v>0.7022332549095154</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3193633258342743</v>
+        <v>0.5771862268447876</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1056103706359863</v>
+        <v>0.1188693046569824</v>
       </c>
       <c r="K3" t="n">
-        <v>75.06952428817749</v>
+        <v>75.01422452926636</v>
       </c>
       <c r="L3" t="n">
-        <v>2.174579858779907</v>
+        <v>2.147994995117188</v>
       </c>
       <c r="M3" t="n">
-        <v>5.869592666625977</v>
+        <v>5.386161804199219</v>
       </c>
       <c r="N3" t="n">
-        <v>13.39125847816467</v>
+        <v>13.21609878540039</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3624299764633178</v>
+        <v>0.3579991658528645</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9782654444376628</v>
+        <v>0.8976936340332031</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.231876413027445</v>
+        <v>2.202683130900065</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-202556</t>
+          <t>20250722-031302</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>74.33053302764893</v>
+        <v>131.6694886684418</v>
       </c>
       <c r="D4" t="n">
-        <v>6.440000057220459</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2969598157690206</v>
+        <v>0.2931424888534162</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7016305923461914</v>
+        <v>0.7559125423431396</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7016305923461914</v>
+        <v>0.7559125423431396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7042144536972046</v>
+        <v>0.7595592141151428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5678380727767944</v>
+        <v>0.3589236140251159</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1074450016021728</v>
+        <v>0.0975794792175293</v>
       </c>
       <c r="K4" t="n">
-        <v>81.5532557964325</v>
+        <v>80.79348206520081</v>
       </c>
       <c r="L4" t="n">
-        <v>2.186485290527344</v>
+        <v>1.861423015594482</v>
       </c>
       <c r="M4" t="n">
-        <v>5.641492605209351</v>
+        <v>5.622387886047363</v>
       </c>
       <c r="N4" t="n">
-        <v>13.1341598033905</v>
+        <v>13.20612001419067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3644142150878906</v>
+        <v>0.310237169265747</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9402487675348916</v>
+        <v>0.9370646476745604</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.189026633898417</v>
+        <v>2.201020002365112</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-203020</t>
+          <t>20250722-031750</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>70.88654923439026</v>
+        <v>131.4919612407684</v>
       </c>
       <c r="D5" t="n">
         <v>6.440000057220459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2945096492767334</v>
+        <v>0.2966061536990218</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7243276834487915</v>
+        <v>0.6895979642868042</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7243276834487915</v>
+        <v>0.6895979642868042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7237601280212402</v>
+        <v>0.6905391216278076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6212132573127747</v>
+        <v>0.6669259071350098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1059508323669433</v>
+        <v>0.1056909561157226</v>
       </c>
       <c r="K5" t="n">
-        <v>75.07425951957703</v>
+        <v>75.22892141342163</v>
       </c>
       <c r="L5" t="n">
-        <v>2.195559978485107</v>
+        <v>2.225499153137207</v>
       </c>
       <c r="M5" t="n">
-        <v>5.336035013198853</v>
+        <v>5.290696144104004</v>
       </c>
       <c r="N5" t="n">
-        <v>13.08971524238586</v>
+        <v>13.48504328727722</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3659266630808512</v>
+        <v>0.3709165255228678</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8893391688664755</v>
+        <v>0.8817826906840006</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.181619207064311</v>
+        <v>2.247507214546204</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-203448</t>
+          <t>20250722-032314</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C6" t="n">
-        <v>74.88798022270203</v>
+        <v>93.84265065193176</v>
       </c>
       <c r="D6" t="n">
-        <v>6.440000057220459</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2938411738894401</v>
+        <v>0.2984910234272909</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6376839876174927</v>
+        <v>0.6861884593963623</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6376839876174927</v>
+        <v>0.6861884593963623</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6390697956085205</v>
+        <v>0.6845965981483459</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6157055497169495</v>
+        <v>0.5411220788955688</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0944783687591552</v>
+        <v>0.1048150062561035</v>
       </c>
       <c r="K6" t="n">
-        <v>74.98932862281799</v>
+        <v>75.31363344192505</v>
       </c>
       <c r="L6" t="n">
-        <v>2.141307830810547</v>
+        <v>2.217852830886841</v>
       </c>
       <c r="M6" t="n">
-        <v>5.339681386947632</v>
+        <v>5.351993799209595</v>
       </c>
       <c r="N6" t="n">
-        <v>13.47277593612671</v>
+        <v>13.05358624458313</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3568846384684245</v>
+        <v>0.3696421384811401</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8899468978246053</v>
+        <v>0.8919989665349325</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.245462656021118</v>
+        <v>2.175597707430521</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-203911</t>
+          <t>20250722-032818</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C2" t="n">
-        <v>63.26079678535461</v>
+        <v>82.55935788154602</v>
       </c>
       <c r="D2" t="n">
         <v>5.820000171661377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1637446146744948</v>
+        <v>0.1640255682998233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6021657586097717</v>
+        <v>0.5981106758117676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6021657586097717</v>
+        <v>0.5981106758117676</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6030622720718384</v>
+        <v>0.5979344844818115</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5793560743331909</v>
+        <v>0.5783673524856567</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0654335021972656</v>
+        <v>0.0669307708740234</v>
       </c>
       <c r="K2" t="n">
-        <v>28.89270401000977</v>
+        <v>22.41000199317932</v>
       </c>
       <c r="L2" t="n">
-        <v>1.675353050231934</v>
+        <v>1.636009216308594</v>
       </c>
       <c r="M2" t="n">
-        <v>3.402865886688232</v>
+        <v>3.102347850799561</v>
       </c>
       <c r="N2" t="n">
-        <v>6.037841558456421</v>
+        <v>5.942945957183838</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2792255083719889</v>
+        <v>0.2726682027180989</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5671443144480387</v>
+        <v>0.5170579751332601</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.006306926409404</v>
+        <v>0.990490992863973</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-130717</t>
+          <t>20250722-205001</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C3" t="n">
-        <v>64.45986437797546</v>
+        <v>70.70410370826721</v>
       </c>
       <c r="D3" t="n">
-        <v>5.670000076293945</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1640304349935971</v>
+        <v>0.162465916525933</v>
       </c>
       <c r="F3" t="n">
-        <v>0.607353687286377</v>
+        <v>0.6103167533874512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.607353687286377</v>
+        <v>0.6103167533874512</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6061220169067383</v>
+        <v>0.6064885854721069</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5966941118240356</v>
+        <v>0.5706509351730347</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06619572639465331</v>
+        <v>0.0649318695068359</v>
       </c>
       <c r="K3" t="n">
-        <v>28.85757541656494</v>
+        <v>28.69703006744385</v>
       </c>
       <c r="L3" t="n">
-        <v>1.678111553192139</v>
+        <v>1.88857889175415</v>
       </c>
       <c r="M3" t="n">
-        <v>3.096876859664917</v>
+        <v>3.082608222961426</v>
       </c>
       <c r="N3" t="n">
-        <v>6.315009355545044</v>
+        <v>6.299825668334961</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2796852588653564</v>
+        <v>0.3147631486256917</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5161461432774862</v>
+        <v>0.5137680371602377</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.052501559257507</v>
+        <v>1.049970944722493</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-131000</t>
+          <t>20250722-205302</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="n">
-        <v>63.34784054756165</v>
+        <v>75.03172969818115</v>
       </c>
       <c r="D4" t="n">
-        <v>5.760000228881836</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1637373612477229</v>
+        <v>0.1634747309069479</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6023575067520142</v>
+        <v>0.607049286365509</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6023575067520142</v>
+        <v>0.607049286365509</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6032167077064514</v>
+        <v>0.6088216304779053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6009799838066101</v>
+        <v>0.6010334491729736</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0633418560028076</v>
+        <v>0.0650856494903564</v>
       </c>
       <c r="K4" t="n">
-        <v>28.13618898391724</v>
+        <v>28.32433652877808</v>
       </c>
       <c r="L4" t="n">
-        <v>1.651325702667236</v>
+        <v>1.601655244827271</v>
       </c>
       <c r="M4" t="n">
-        <v>3.086149930953979</v>
+        <v>3.099500894546509</v>
       </c>
       <c r="N4" t="n">
-        <v>6.332332372665405</v>
+        <v>5.909929275512695</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2752209504445393</v>
+        <v>0.2669425408045451</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5143583218256632</v>
+        <v>0.5165834824244181</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.055388728777568</v>
+        <v>0.9849882125854492</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-131244</t>
+          <t>20250722-205553</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C5" t="n">
-        <v>63.18796515464783</v>
+        <v>79.93235421180725</v>
       </c>
       <c r="D5" t="n">
-        <v>5.670000076293945</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1631972537590907</v>
+        <v>0.165967750905165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6067825555801392</v>
+        <v>0.6067294478416443</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6067825555801392</v>
+        <v>0.6067294478416443</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6072930097579956</v>
+        <v>0.607621431350708</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5808786153793335</v>
+        <v>0.5992969274520874</v>
       </c>
       <c r="J5" t="n">
-        <v>0.064166784286499</v>
+        <v>0.0643019676208496</v>
       </c>
       <c r="K5" t="n">
-        <v>22.9380738735199</v>
+        <v>22.41265296936035</v>
       </c>
       <c r="L5" t="n">
-        <v>1.687938451766968</v>
+        <v>1.610543251037598</v>
       </c>
       <c r="M5" t="n">
-        <v>3.119208335876465</v>
+        <v>3.016154289245605</v>
       </c>
       <c r="N5" t="n">
-        <v>5.853946447372437</v>
+        <v>6.017009973526001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2813230752944946</v>
+        <v>0.2684238751729329</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5198680559794108</v>
+        <v>0.5026923815409342</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9756577412287394</v>
+        <v>1.002834995587667</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-131526</t>
+          <t>20250722-205847</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C6" t="n">
-        <v>69.11628746986389</v>
+        <v>81.34440875053406</v>
       </c>
       <c r="D6" t="n">
         <v>5.760000228881836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1632873886509945</v>
+        <v>0.1654283245690434</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6021234393119812</v>
+        <v>0.6002553105354309</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6021234393119812</v>
+        <v>0.6002553105354309</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6043533086776733</v>
+        <v>0.6021208763122559</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5893096327781677</v>
+        <v>0.5985835790634155</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0661025047302246</v>
+        <v>0.0652503967285156</v>
       </c>
       <c r="K6" t="n">
-        <v>28.6200053691864</v>
+        <v>23.22027802467347</v>
       </c>
       <c r="L6" t="n">
-        <v>1.602016925811768</v>
+        <v>1.613204479217529</v>
       </c>
       <c r="M6" t="n">
-        <v>3.028592586517334</v>
+        <v>3.094518899917603</v>
       </c>
       <c r="N6" t="n">
-        <v>6.294787168502808</v>
+        <v>5.915699243545532</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2670028209686279</v>
+        <v>0.2688674132029215</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5047654310862223</v>
+        <v>0.5157531499862671</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.049131194750468</v>
+        <v>0.9859498739242554</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-131808</t>
+          <t>20250722-210146</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>46.9076361656189</v>
+        <v>54.08006620407104</v>
       </c>
       <c r="D2" t="n">
         <v>3.339999914169312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1025969500725085</v>
+        <v>0.1038416912478785</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6103848814964294</v>
+        <v>0.6112062931060791</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6103848814964294</v>
+        <v>0.6112062931060791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6105414032936096</v>
+        <v>0.6117129325866699</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6151244640350342</v>
+        <v>0.6003451943397522</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0412719249725341</v>
+        <v>0.0438613891601562</v>
       </c>
       <c r="K2" t="n">
-        <v>18.02299404144287</v>
+        <v>12.86096405982971</v>
       </c>
       <c r="L2" t="n">
-        <v>1.061752080917358</v>
+        <v>1.091675281524658</v>
       </c>
       <c r="M2" t="n">
-        <v>2.033459901809692</v>
+        <v>2.056397914886475</v>
       </c>
       <c r="N2" t="n">
-        <v>3.46581244468689</v>
+        <v>3.572927474975586</v>
       </c>
       <c r="O2" t="n">
-        <v>0.176958680152893</v>
+        <v>0.1819458802541097</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3389099836349487</v>
+        <v>0.3427329858144124</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5776354074478149</v>
+        <v>0.595487912495931</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-193810</t>
+          <t>20250723-042310</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C3" t="n">
-        <v>54.55430269241333</v>
+        <v>56.22017645835876</v>
       </c>
       <c r="D3" t="n">
-        <v>3.339999914169312</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1040061289264309</v>
+        <v>0.1039638149645901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5965043306350708</v>
+        <v>0.6099528074264526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5965043306350708</v>
+        <v>0.6099528074264526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5969869494438171</v>
+        <v>0.6104981899261475</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5985857248306274</v>
+        <v>0.6016044616699219</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0436048507690429</v>
+        <v>0.0430245399475097</v>
       </c>
       <c r="K3" t="n">
-        <v>18.21030855178833</v>
+        <v>18.45118594169617</v>
       </c>
       <c r="L3" t="n">
-        <v>1.124585390090942</v>
+        <v>1.136976718902588</v>
       </c>
       <c r="M3" t="n">
-        <v>2.436961650848389</v>
+        <v>2.108597040176392</v>
       </c>
       <c r="N3" t="n">
-        <v>3.434296607971191</v>
+        <v>3.464010238647461</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1874308983484904</v>
+        <v>0.189496119817098</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4061602751413981</v>
+        <v>0.3514328400293986</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5723827679951986</v>
+        <v>0.5773350397745768</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-194012</t>
+          <t>20250723-042520</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="n">
-        <v>45.530118227005</v>
+        <v>53.4193868637085</v>
       </c>
       <c r="D4" t="n">
-        <v>3.490000009536743</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.103894653228613</v>
+        <v>0.1054024446395135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6085318326950073</v>
+        <v>0.6082779765129089</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6085318326950073</v>
+        <v>0.6082779765129089</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6074460744857788</v>
+        <v>0.6081500053405762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6042457818984985</v>
+        <v>0.5372636318206787</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0426352024078369</v>
+        <v>0.0429873466491699</v>
       </c>
       <c r="K4" t="n">
-        <v>18.3168158531189</v>
+        <v>18.32848930358887</v>
       </c>
       <c r="L4" t="n">
-        <v>1.131932258605957</v>
+        <v>1.097275733947754</v>
       </c>
       <c r="M4" t="n">
-        <v>2.424085378646851</v>
+        <v>2.051932811737061</v>
       </c>
       <c r="N4" t="n">
-        <v>3.492770671844482</v>
+        <v>3.492421865463257</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1886553764343261</v>
+        <v>0.1828792889912923</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4040142297744751</v>
+        <v>0.3419888019561767</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5821284453074137</v>
+        <v>0.5820703109105428</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-194222</t>
+          <t>20250723-042732</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>47.91543698310852</v>
+        <v>52.43561673164368</v>
       </c>
       <c r="D5" t="n">
-        <v>3.400000095367432</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1055380083047426</v>
+        <v>0.1043470694172766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6126317977905273</v>
+        <v>0.6190581321716309</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6126317977905273</v>
+        <v>0.6190581321716309</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6111290454864502</v>
+        <v>0.619173526763916</v>
       </c>
       <c r="I5" t="n">
-        <v>0.33187997341156</v>
+        <v>0.6115881204605103</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0411770343780517</v>
+        <v>0.0417466163635253</v>
       </c>
       <c r="K5" t="n">
-        <v>18.04408478736877</v>
+        <v>18.39608263969421</v>
       </c>
       <c r="L5" t="n">
-        <v>1.099365472793579</v>
+        <v>1.10228681564331</v>
       </c>
       <c r="M5" t="n">
-        <v>2.029290914535522</v>
+        <v>2.346129655838013</v>
       </c>
       <c r="N5" t="n">
-        <v>3.470319032669067</v>
+        <v>3.505088806152344</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1832275787989298</v>
+        <v>0.1837144692738851</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3382151524225871</v>
+        <v>0.3910216093063354</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5783865054448446</v>
+        <v>0.5841814676920573</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-194424</t>
+          <t>20250723-042942</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="C6" t="n">
-        <v>48.34620404243469</v>
+        <v>64.96822953224182</v>
       </c>
       <c r="D6" t="n">
-        <v>3.490000009536743</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1041637407530338</v>
+        <v>0.1046317908670994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5979527831077576</v>
+        <v>0.6163947582244873</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5979527831077576</v>
+        <v>0.6163947582244873</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5970353484153748</v>
+        <v>0.6160926818847656</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6014353632926941</v>
+        <v>0.5342826843261719</v>
       </c>
       <c r="J6" t="n">
-        <v>0.041935920715332</v>
+        <v>0.0502185821533203</v>
       </c>
       <c r="K6" t="n">
-        <v>12.88816380500794</v>
+        <v>18.21763634681702</v>
       </c>
       <c r="L6" t="n">
-        <v>1.061025857925415</v>
+        <v>1.182928085327148</v>
       </c>
       <c r="M6" t="n">
-        <v>2.067927598953247</v>
+        <v>2.041628360748291</v>
       </c>
       <c r="N6" t="n">
-        <v>3.424293041229248</v>
+        <v>3.445764064788818</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1768376429875691</v>
+        <v>0.197154680887858</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3446545998255412</v>
+        <v>0.3402713934580485</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5707155068715414</v>
+        <v>0.5742940107981364</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-194628</t>
+          <t>20250723-043151</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5220,53 +5220,53 @@
         <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>47.55352854728699</v>
+        <v>47.66201949119568</v>
       </c>
       <c r="D2" t="n">
-        <v>2.230000019073486</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="E2" t="n">
-        <v>0.104133992425857</v>
+        <v>0.1070312338490639</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6179323196411133</v>
+        <v>0.6063363552093506</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6179323196411133</v>
+        <v>0.6063363552093506</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6213950514793396</v>
+        <v>0.6064466238021851</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6160985231399536</v>
+        <v>0.6103628873825073</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0379393100738525</v>
+        <v>0.0395128726959228</v>
       </c>
       <c r="K2" t="n">
-        <v>17.9989812374115</v>
+        <v>17.85538840293884</v>
       </c>
       <c r="L2" t="n">
-        <v>0.961467981338501</v>
+        <v>0.9951660633087158</v>
       </c>
       <c r="M2" t="n">
-        <v>2.05432391166687</v>
+        <v>2.013684988021851</v>
       </c>
       <c r="N2" t="n">
-        <v>3.712939262390137</v>
+        <v>3.719270944595337</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1602446635564168</v>
+        <v>0.1658610105514526</v>
       </c>
       <c r="P2" t="n">
-        <v>0.342387318611145</v>
+        <v>0.3356141646703084</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6188232103983561</v>
+        <v>0.6198784907658895</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-000113</t>
+          <t>20250723-095606</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C3" t="n">
-        <v>40.41632771492005</v>
+        <v>51.8796808719635</v>
       </c>
       <c r="D3" t="n">
-        <v>2.440000057220459</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1059268781772026</v>
+        <v>0.1059032838736007</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6137626171112061</v>
+        <v>0.6004121899604797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6137626171112061</v>
+        <v>0.6004121899604797</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6124452352523804</v>
+        <v>0.6017460823059082</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6178182363510132</v>
+        <v>0.6007483005523682</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0413196086883544</v>
+        <v>0.0391943454742431</v>
       </c>
       <c r="K3" t="n">
-        <v>18.06377530097961</v>
+        <v>17.91910409927368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.971670150756836</v>
+        <v>0.9874813556671144</v>
       </c>
       <c r="M3" t="n">
-        <v>2.041831254959106</v>
+        <v>1.99739146232605</v>
       </c>
       <c r="N3" t="n">
-        <v>3.755629301071167</v>
+        <v>3.784570455551148</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1619450251261393</v>
+        <v>0.164580225944519</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3403052091598511</v>
+        <v>0.3328985770543416</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6259382168451945</v>
+        <v>0.6307617425918579</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-000316</t>
+          <t>20250723-095810</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C4" t="n">
-        <v>46.29108881950378</v>
+        <v>50.52325844764709</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190000057220459</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1050979514275827</v>
+        <v>0.1028209657811406</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6040718555450439</v>
+        <v>0.6113154888153076</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6040718555450439</v>
+        <v>0.6113154888153076</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6022583842277527</v>
+        <v>0.6126788854598999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5977650284767151</v>
+        <v>0.6167751550674438</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0411028861999511</v>
+        <v>0.0370206832885742</v>
       </c>
       <c r="K4" t="n">
-        <v>17.90604543685913</v>
+        <v>17.55329394340515</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01902961730957</v>
+        <v>0.965627908706665</v>
       </c>
       <c r="M4" t="n">
-        <v>2.344335556030273</v>
+        <v>2.03062105178833</v>
       </c>
       <c r="N4" t="n">
-        <v>4.080416202545166</v>
+        <v>3.753409862518311</v>
       </c>
       <c r="O4" t="n">
-        <v>0.169838269551595</v>
+        <v>0.1609379847844441</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907225926717122</v>
+        <v>0.3384368419647217</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.680069367090861</v>
+        <v>0.6255683104197184</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-000513</t>
+          <t>20250723-100018</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="C5" t="n">
-        <v>44.06217861175537</v>
+        <v>56.88245582580566</v>
       </c>
       <c r="D5" t="n">
-        <v>2.230000019073486</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1046937829569766</v>
+        <v>0.1059146391880976</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6155451536178589</v>
+        <v>0.6119639277458191</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6155451536178589</v>
+        <v>0.6119639277458191</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6144675016403198</v>
+        <v>0.6127537488937378</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6112265586853027</v>
+        <v>0.6113439202308655</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0413377285003662</v>
+        <v>0.0425105094909668</v>
       </c>
       <c r="K5" t="n">
-        <v>12.19975256919861</v>
+        <v>17.69224858283997</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9769768714904784</v>
+        <v>1.010120630264282</v>
       </c>
       <c r="M5" t="n">
-        <v>1.99467921257019</v>
+        <v>2.057066202163696</v>
       </c>
       <c r="N5" t="n">
-        <v>3.787367582321167</v>
+        <v>4.075538158416748</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1628294785817464</v>
+        <v>0.1683534383773803</v>
       </c>
       <c r="P5" t="n">
-        <v>0.332446535428365</v>
+        <v>0.3428443670272827</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6312279303868612</v>
+        <v>0.6792563597361246</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-000716</t>
+          <t>20250723-100225</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
-        <v>45.21643090248108</v>
+        <v>50.37387371063232</v>
       </c>
       <c r="D6" t="n">
         <v>2.190000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.104214924724162</v>
+        <v>0.1057289536319561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6110843420028687</v>
+        <v>0.60679030418396</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6110843420028687</v>
+        <v>0.60679030418396</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6127482056617737</v>
+        <v>0.6063095331192017</v>
       </c>
       <c r="I6" t="n">
-        <v>0.608864426612854</v>
+        <v>0.6066809296607971</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0440285205841064</v>
+        <v>0.0418615341186523</v>
       </c>
       <c r="K6" t="n">
-        <v>17.77091097831726</v>
+        <v>17.51629161834717</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9900259971618652</v>
+        <v>0.989842414855957</v>
       </c>
       <c r="M6" t="n">
-        <v>2.033800363540649</v>
+        <v>1.996562242507934</v>
       </c>
       <c r="N6" t="n">
-        <v>4.153174877166748</v>
+        <v>3.824278116226196</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1650043328603108</v>
+        <v>0.1649737358093261</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3389667272567749</v>
+        <v>0.3327603737513224</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6921958128611246</v>
+        <v>0.6373796860376993</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-000916</t>
+          <t>20250723-100438</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
